--- a/Data/FlightPlan/FPL_13SEP26.xlsx
+++ b/Data/FlightPlan/FPL_13SEP26.xlsx
@@ -74,528 +74,543 @@
     <t>07:30</t>
   </si>
   <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A201</t>
+  </si>
+  <si>
+    <t>HAN</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>14/09/26</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A202</t>
+  </si>
+  <si>
+    <t>SGN</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
     <t>10:10</t>
   </si>
   <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A201</t>
-  </si>
-  <si>
-    <t>HAN</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>14/09/26</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A202</t>
-  </si>
-  <si>
-    <t>SGN</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
     <t>13:50</t>
   </si>
   <si>
@@ -818,6 +833,9 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>09:42</t>
+  </si>
+  <si>
     <t>14:45</t>
   </si>
   <si>
@@ -962,6 +980,9 @@
     <t>HIJ</t>
   </si>
   <si>
+    <t>12:21</t>
+  </si>
+  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -995,6 +1016,9 @@
     <t>05:20</t>
   </si>
   <si>
+    <t>06:37</t>
+  </si>
+  <si>
     <t>ENH</t>
   </si>
   <si>
@@ -1025,6 +1049,9 @@
     <t>VN-A658</t>
   </si>
   <si>
+    <t>07:19</t>
+  </si>
+  <si>
     <t>07:40</t>
   </si>
   <si>
@@ -1061,12 +1088,18 @@
     <t>07:45</t>
   </si>
   <si>
+    <t>09:59</t>
+  </si>
+  <si>
     <t>20:40</t>
   </si>
   <si>
     <t>VN-A671</t>
   </si>
   <si>
+    <t>07:06</t>
+  </si>
+  <si>
     <t>VN-A672</t>
   </si>
   <si>
@@ -1091,6 +1124,9 @@
     <t>VN-A675</t>
   </si>
   <si>
+    <t>07:41</t>
+  </si>
+  <si>
     <t>VN-A676</t>
   </si>
   <si>
@@ -1106,6 +1142,9 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>06:59</t>
+  </si>
+  <si>
     <t>01:05</t>
   </si>
   <si>
@@ -1130,6 +1169,9 @@
     <t>05:45</t>
   </si>
   <si>
+    <t>07:27</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
@@ -1211,7 +1253,7 @@
     <t>Total Record(s): 379</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 13, 2026 02:58</t>
+    <t xml:space="preserve">Generated on  Sep 13, 2026 06:10</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2644,7 +2686,9 @@
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
+      <c t="s" r="M36" s="7">
+        <v>83</v>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c t="s" r="A37" s="6">
@@ -2670,10 +2714,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2706,7 +2750,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2736,10 +2780,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2766,10 +2810,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J40" s="7">
         <v>49</v>
@@ -2796,16 +2840,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2832,10 +2876,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>25</v>
@@ -2862,7 +2906,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>41</v>
@@ -2871,7 +2915,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2904,7 +2948,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2913,13 +2957,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2937,22 +2981,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2970,7 +3014,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2979,13 +3023,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3003,13 +3047,13 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>41</v>
@@ -3018,7 +3062,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3036,7 +3080,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3045,13 +3089,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="I49" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3084,7 +3128,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3096,14 +3140,16 @@
         <v>42</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c t="s" r="M51" s="7">
+        <v>110</v>
+      </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c t="s" r="A52" s="6">
@@ -3117,7 +3163,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3126,13 +3172,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3150,22 +3196,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3183,7 +3229,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3195,7 +3241,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>31</v>
@@ -3216,7 +3262,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3225,13 +3271,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I55" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3249,22 +3295,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3282,7 +3328,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3291,13 +3337,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I57" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3315,22 +3361,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3363,7 +3409,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3375,10 +3421,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3396,7 +3442,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3405,13 +3451,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3429,22 +3475,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3462,7 +3508,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3471,10 +3517,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>43</v>
@@ -3510,7 +3556,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3522,10 +3568,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3543,7 +3589,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3555,10 +3601,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3591,7 +3637,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3603,14 +3649,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c t="s" r="M68" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
@@ -3624,7 +3672,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3636,10 +3684,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3657,7 +3705,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3666,13 +3714,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I70" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3690,19 +3738,19 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>50</v>
@@ -3723,7 +3771,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3735,7 +3783,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>78</v>
@@ -3756,7 +3804,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3765,13 +3813,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3789,22 +3837,22 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3837,7 +3885,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3846,13 +3894,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3870,22 +3918,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3903,7 +3951,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3912,13 +3960,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3936,22 +3984,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3969,7 +4017,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3978,13 +4026,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I80" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4002,22 +4050,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4035,7 +4083,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4047,10 +4095,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4068,7 +4116,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4080,10 +4128,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4116,7 +4164,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4128,17 +4176,17 @@
         <v>41</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4153,7 +4201,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4162,13 +4210,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4186,19 +4234,19 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>79</v>
@@ -4219,7 +4267,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4231,10 +4279,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4267,7 +4315,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4279,14 +4327,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>164</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
@@ -4300,7 +4350,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4312,10 +4362,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4333,7 +4383,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4345,10 +4395,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4366,7 +4416,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4381,7 +4431,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4399,7 +4449,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4411,10 +4461,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4447,7 +4497,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4456,13 +4506,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4480,19 +4530,19 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>53</v>
@@ -4513,7 +4563,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4528,7 +4578,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4546,7 +4596,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4558,10 +4608,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4579,7 +4629,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4588,13 +4638,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4612,22 +4662,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4645,7 +4695,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4657,7 +4707,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>63</v>
@@ -4693,7 +4743,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4702,13 +4752,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4726,22 +4776,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4774,7 +4824,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4786,10 +4836,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4807,7 +4857,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4819,10 +4869,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4840,7 +4890,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4852,10 +4902,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4873,7 +4923,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4885,10 +4935,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4906,7 +4956,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4921,7 +4971,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4954,7 +5004,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4966,10 +5016,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4987,7 +5037,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4999,10 +5049,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5020,7 +5070,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5029,13 +5079,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5053,22 +5103,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5086,7 +5136,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5098,7 +5148,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>43</v>
@@ -5130,33 +5180,33 @@
         <v>7659</v>
       </c>
       <c t="s" r="C119" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5167,11 +5217,11 @@
         <v>7659</v>
       </c>
       <c t="s" r="C120" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5183,17 +5233,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="K120" s="7">
         <v>48</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5208,7 +5258,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5220,10 +5270,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5241,7 +5291,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5256,7 +5306,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5274,7 +5324,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5286,10 +5336,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5322,22 +5372,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5355,7 +5405,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5367,7 +5417,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>64</v>
@@ -5403,7 +5453,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5415,10 +5465,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5436,7 +5486,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5445,13 +5495,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5469,13 +5519,13 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>28</v>
@@ -5484,7 +5534,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5502,7 +5552,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5514,10 +5564,10 @@
         <v>67</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5550,7 +5600,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5559,20 +5609,20 @@
         <v>59</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5587,19 +5637,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>38</v>
@@ -5620,7 +5670,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5629,13 +5679,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5668,7 +5718,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5680,10 +5730,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5701,7 +5751,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5713,10 +5763,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5730,11 +5780,11 @@
         <v>2924</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5746,10 +5796,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5763,11 +5813,11 @@
         <v>2924</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5776,13 +5826,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5796,23 +5846,23 @@
         <v>2925</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>69</v>
@@ -5848,22 +5898,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
+        <v>219</v>
+      </c>
+      <c r="F143" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G143" s="8">
         <v>214</v>
-      </c>
-      <c r="F143" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G143" s="8">
-        <v>209</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5881,7 +5931,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5890,13 +5940,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5910,23 +5960,23 @@
         <v>7614</v>
       </c>
       <c t="s" r="C145" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>25</v>
@@ -5943,11 +5993,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C146" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5956,13 +6006,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5995,7 +6045,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6007,15 +6057,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6030,7 +6080,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6045,7 +6095,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6063,7 +6113,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6075,10 +6125,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6096,7 +6146,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6108,10 +6158,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6129,7 +6179,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6141,7 +6191,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>19</v>
@@ -6177,7 +6227,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6189,14 +6239,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>18</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
+      <c t="s" r="M154" s="7">
+        <v>160</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c t="s" r="A155" s="6">
@@ -6210,7 +6262,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6225,7 +6277,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6243,7 +6295,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6255,10 +6307,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6276,7 +6328,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6285,13 +6337,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6309,19 +6361,19 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>24</v>
@@ -6342,7 +6394,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6351,10 +6403,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>66</v>
@@ -6375,22 +6427,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6423,7 +6475,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6435,17 +6487,17 @@
         <v>41</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c t="s" r="K162" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>144</v>
+        <v>201</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6460,7 +6512,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6475,7 +6527,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6493,7 +6545,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6505,7 +6557,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>24</v>
@@ -6526,7 +6578,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6535,13 +6587,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6559,22 +6611,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6607,7 +6659,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6616,13 +6668,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6640,13 +6692,13 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>41</v>
@@ -6655,7 +6707,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6688,7 +6740,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6697,13 +6749,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6721,13 +6773,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>41</v>
@@ -6736,7 +6788,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6754,7 +6806,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6763,10 +6815,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>68</v>
@@ -6787,22 +6839,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6835,7 +6887,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6844,13 +6896,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6868,19 +6920,19 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>69</v>
@@ -6901,7 +6953,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6913,7 +6965,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>23</v>
@@ -6934,7 +6986,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6946,7 +6998,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>65</v>
@@ -6967,7 +7019,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6976,13 +7028,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7000,22 +7052,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7033,7 +7085,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7045,10 +7097,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7066,7 +7118,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7078,10 +7130,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7114,7 +7166,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7126,10 +7178,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7147,7 +7199,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7156,7 +7208,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>33</v>
@@ -7180,19 +7232,19 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>44</v>
@@ -7228,7 +7280,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7240,7 +7292,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>69</v>
@@ -7261,7 +7313,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7273,7 +7325,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>45</v>
@@ -7294,7 +7346,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7303,13 +7355,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7327,22 +7379,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7360,7 +7412,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7369,13 +7421,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7393,22 +7445,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7441,7 +7493,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7450,13 +7502,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7474,22 +7526,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7507,7 +7559,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7519,10 +7571,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7540,7 +7592,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7552,7 +7604,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>75</v>
@@ -7573,7 +7625,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7582,10 +7634,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>56</v>
@@ -7606,22 +7658,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7639,7 +7691,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7648,10 +7700,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>51</v>
@@ -7672,22 +7724,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7720,7 +7772,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7729,17 +7781,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>274</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
@@ -7753,22 +7807,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7786,7 +7840,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7798,10 +7852,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7819,7 +7873,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7831,10 +7885,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7852,7 +7906,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7864,10 +7918,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7885,7 +7939,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7897,10 +7951,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7933,7 +7987,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7942,13 +7996,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7966,22 +8020,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7999,7 +8053,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8008,13 +8062,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8032,13 +8086,13 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>28</v>
@@ -8047,7 +8101,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8065,7 +8119,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8077,10 +8131,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8098,7 +8152,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8110,7 +8164,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>51</v>
@@ -8146,7 +8200,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8155,13 +8209,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8179,22 +8233,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8212,7 +8266,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8221,13 +8275,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8245,22 +8299,22 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8278,22 +8332,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8311,22 +8365,22 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8359,7 +8413,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8368,17 +8422,21 @@
         <v>41</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>84</v>
-      </c>
-      <c r="K226" s="7"/>
+        <v>85</v>
+      </c>
+      <c t="s" r="K226" s="7">
+        <v>190</v>
+      </c>
       <c r="L226" s="7"/>
-      <c r="M226" s="7"/>
+      <c t="s" r="M226" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c t="s" r="A227" s="6">
@@ -8392,13 +8450,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>41</v>
@@ -8407,11 +8465,15 @@
         <v>30</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>178</v>
-      </c>
-      <c r="K227" s="7"/>
+        <v>182</v>
+      </c>
+      <c t="s" r="K227" s="7">
+        <v>101</v>
+      </c>
       <c r="L227" s="7"/>
-      <c r="M227" s="7"/>
+      <c t="s" r="M227" s="7">
+        <v>206</v>
+      </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
@@ -8425,7 +8487,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8434,13 +8496,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8458,22 +8520,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8491,7 +8553,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8500,10 +8562,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>50</v>
@@ -8524,13 +8586,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>41</v>
@@ -8539,7 +8601,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8557,7 +8619,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8569,7 +8631,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>58</v>
@@ -8590,7 +8652,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8602,10 +8664,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8638,7 +8700,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8650,10 +8712,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8671,7 +8733,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8683,10 +8745,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8719,7 +8781,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8728,13 +8790,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8752,22 +8814,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8785,7 +8847,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8794,13 +8856,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8818,22 +8880,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8851,7 +8913,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8863,7 +8925,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>66</v>
@@ -8899,7 +8961,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8911,10 +8973,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8932,7 +8994,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8944,10 +9006,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8965,7 +9027,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8977,10 +9039,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8998,7 +9060,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9010,10 +9072,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9046,7 +9108,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9055,17 +9117,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
-      <c r="M249" s="7"/>
+      <c t="s" r="M249" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c t="s" r="A250" s="6">
@@ -9079,22 +9143,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9112,22 +9176,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9145,22 +9209,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9178,7 +9242,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9190,7 +9254,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>78</v>
@@ -9211,7 +9275,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9223,10 +9287,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9259,22 +9323,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9292,7 +9356,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9301,13 +9365,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9325,22 +9389,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9358,7 +9422,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9370,7 +9434,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>63</v>
@@ -9406,7 +9470,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9415,7 +9479,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>20</v>
@@ -9439,22 +9503,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9472,7 +9536,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9481,13 +9545,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9505,22 +9569,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9538,7 +9602,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9547,13 +9611,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9571,22 +9635,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9619,7 +9683,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9631,10 +9695,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9652,7 +9716,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9667,7 +9731,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9685,7 +9749,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9700,7 +9764,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9733,7 +9797,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9745,10 +9809,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9766,7 +9830,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9778,10 +9842,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9799,7 +9863,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9811,10 +9875,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9832,7 +9896,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9841,13 +9905,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9865,22 +9929,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9913,7 +9977,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9922,17 +9986,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>74</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
-      <c r="M278" s="7"/>
+      <c t="s" r="M278" s="7">
+        <v>323</v>
+      </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
@@ -9946,22 +10012,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9979,7 +10045,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -9988,10 +10054,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>25</v>
@@ -10012,13 +10078,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>28</v>
@@ -10027,7 +10093,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10060,7 +10126,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10072,10 +10138,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10093,7 +10159,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10102,7 +10168,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>45</v>
@@ -10126,13 +10192,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>28</v>
@@ -10141,7 +10207,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10159,7 +10225,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10168,13 +10234,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10192,22 +10258,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10225,7 +10291,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10237,10 +10303,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10273,7 +10339,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10282,10 +10348,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>20</v>
@@ -10306,13 +10372,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>41</v>
@@ -10321,7 +10387,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10339,7 +10405,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10348,13 +10414,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10372,22 +10438,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10405,7 +10471,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10414,7 +10480,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>65</v>
@@ -10438,22 +10504,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10486,7 +10552,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10495,17 +10561,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>60</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
-      <c r="M297" s="7"/>
+      <c t="s" r="M297" s="7">
+        <v>335</v>
+      </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
       <c t="s" r="A298" s="6">
@@ -10519,19 +10587,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>69</v>
@@ -10552,7 +10620,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10561,13 +10629,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10585,19 +10653,19 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>74</v>
@@ -10618,7 +10686,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10627,13 +10695,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10651,22 +10719,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10699,19 +10767,19 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>32</v>
@@ -10732,7 +10800,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10741,13 +10809,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10765,22 +10833,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10813,7 +10881,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10825,10 +10893,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10846,7 +10914,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10858,7 +10926,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>32</v>
@@ -10879,7 +10947,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10891,7 +10959,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>55</v>
@@ -10912,7 +10980,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10924,10 +10992,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10945,7 +11013,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -10957,17 +11025,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="K312" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -10982,7 +11050,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10994,10 +11062,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11015,7 +11083,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11027,10 +11095,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11063,7 +11131,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11072,17 +11140,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
-      <c r="M316" s="7"/>
+      <c t="s" r="M316" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
       <c t="s" r="A317" s="6">
@@ -11096,22 +11166,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11129,7 +11199,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11138,13 +11208,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H318" s="8">
+        <v>116</v>
+      </c>
+      <c t="s" r="I318" s="7">
         <v>114</v>
       </c>
-      <c t="s" r="I318" s="7">
-        <v>112</v>
-      </c>
       <c t="s" r="J318" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11162,22 +11232,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11195,7 +11265,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11207,10 +11277,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11228,7 +11298,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11240,7 +11310,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>26</v>
@@ -11276,7 +11346,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11309,7 +11379,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11321,10 +11391,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11342,7 +11412,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11351,10 +11421,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>77</v>
@@ -11375,22 +11445,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11408,7 +11478,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11417,13 +11487,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11441,22 +11511,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11489,7 +11559,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11501,10 +11571,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11522,7 +11592,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11531,10 +11601,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>23</v>
@@ -11555,22 +11625,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11588,7 +11658,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11597,13 +11667,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11621,19 +11691,19 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>79</v>
@@ -11669,7 +11739,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11684,7 +11754,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11702,7 +11772,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11717,7 +11787,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11735,7 +11805,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11747,10 +11817,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11768,7 +11838,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11783,7 +11853,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11816,7 +11886,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11828,10 +11898,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11849,7 +11919,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11861,10 +11931,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11882,7 +11952,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11891,13 +11961,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11915,19 +11985,19 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>24</v>
@@ -11963,7 +12033,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -11975,14 +12045,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
-      <c r="M346" s="7"/>
+      <c t="s" r="M346" s="7">
+        <v>359</v>
+      </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
@@ -11996,7 +12068,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12008,10 +12080,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12029,7 +12101,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12041,10 +12113,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12062,7 +12134,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12074,10 +12146,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12110,7 +12182,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12122,14 +12194,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>362</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
@@ -12143,7 +12217,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12155,7 +12229,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>45</v>
@@ -12176,7 +12250,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12185,13 +12259,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12209,22 +12283,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12257,7 +12331,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12266,13 +12340,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12290,22 +12364,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12323,7 +12397,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12332,10 +12406,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>50</v>
@@ -12356,13 +12430,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>41</v>
@@ -12389,7 +12463,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12398,10 +12472,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>79</v>
@@ -12422,22 +12496,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12470,7 +12544,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12479,10 +12553,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>54</v>
@@ -12503,22 +12577,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12551,7 +12625,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12563,13 +12637,13 @@
         <v>41</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>31</v>
       </c>
       <c t="s" r="K366" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
@@ -12588,7 +12662,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12600,10 +12674,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12621,7 +12695,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12633,10 +12707,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12654,7 +12728,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12666,10 +12740,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12702,7 +12776,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12711,17 +12785,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -12735,19 +12811,19 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>44</v>
@@ -12768,7 +12844,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12777,13 +12853,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12801,22 +12877,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12834,7 +12910,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12843,10 +12919,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>50</v>
@@ -12867,22 +12943,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12915,7 +12991,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -12927,14 +13003,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
-      <c r="M378" s="7"/>
+      <c t="s" r="M378" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
@@ -12948,7 +13026,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -12960,10 +13038,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12981,7 +13059,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -12993,10 +13071,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13014,7 +13092,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13026,10 +13104,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13047,7 +13125,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13059,10 +13137,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13080,7 +13158,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13089,10 +13167,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>35</v>
@@ -13113,22 +13191,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13161,7 +13239,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13173,14 +13251,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>18</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
-      <c r="M386" s="7"/>
+      <c t="s" r="M386" s="7">
+        <v>377</v>
+      </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
       <c t="s" r="A387" s="6">
@@ -13194,7 +13274,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13209,7 +13289,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13227,7 +13307,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13236,13 +13316,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13260,22 +13340,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13293,7 +13373,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13308,7 +13388,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13326,7 +13406,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13338,7 +13418,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>50</v>
@@ -13359,7 +13439,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13371,10 +13451,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13392,7 +13472,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13404,10 +13484,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13425,7 +13505,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13437,10 +13517,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13473,7 +13553,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13485,7 +13565,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>74</v>
@@ -13506,7 +13586,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13518,10 +13598,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13539,7 +13619,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13548,13 +13628,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13572,19 +13652,19 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>58</v>
@@ -13620,7 +13700,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13629,10 +13709,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>31</v>
@@ -13653,13 +13733,13 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>28</v>
@@ -13668,7 +13748,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13686,7 +13766,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13695,13 +13775,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13719,22 +13799,22 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13767,7 +13847,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13782,7 +13862,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13800,7 +13880,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13815,7 +13895,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13848,7 +13928,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13857,13 +13937,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13881,22 +13961,22 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13914,7 +13994,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13923,10 +14003,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>55</v>
@@ -13947,22 +14027,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13980,7 +14060,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -13995,7 +14075,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14013,7 +14093,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14025,10 +14105,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14061,7 +14141,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14070,17 +14150,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
-      <c r="M416" s="7"/>
+      <c t="s" r="M416" s="7">
+        <v>386</v>
+      </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
       <c t="s" r="A417" s="6">
@@ -14094,22 +14176,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14127,7 +14209,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -14136,13 +14218,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14160,22 +14242,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14193,7 +14275,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14208,7 +14290,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14226,7 +14308,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14238,10 +14320,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14274,7 +14356,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14286,10 +14368,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14307,7 +14389,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14319,10 +14401,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14340,7 +14422,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14349,13 +14431,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14373,22 +14455,22 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14421,7 +14503,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14430,13 +14512,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14454,22 +14536,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14487,7 +14569,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14499,10 +14581,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14520,7 +14602,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14535,7 +14617,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14553,7 +14635,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14565,10 +14647,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14601,22 +14683,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14634,22 +14716,22 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14667,22 +14749,22 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14700,7 +14782,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14712,10 +14794,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14748,7 +14830,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -14757,13 +14839,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14781,13 +14863,13 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>41</v>
@@ -14814,7 +14896,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -14823,10 +14905,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>64</v>
@@ -14847,22 +14929,22 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14880,7 +14962,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -14892,10 +14974,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14928,7 +15010,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -14940,10 +15022,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -14961,7 +15043,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -14973,7 +15055,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>64</v>
@@ -14994,7 +15076,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15009,7 +15091,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15042,7 +15124,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -15057,7 +15139,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15090,22 +15172,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15123,7 +15205,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15132,13 +15214,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15171,7 +15253,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15180,13 +15262,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15204,22 +15286,22 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15237,22 +15319,22 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15285,7 +15367,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15297,10 +15379,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15333,7 +15415,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15342,13 +15424,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15366,22 +15448,22 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c t="s" r="I461" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15399,22 +15481,22 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15447,7 +15529,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -15456,13 +15538,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15480,22 +15562,22 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15503,7 +15585,7 @@
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c t="s" r="A466" s="9">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
@@ -15523,7 +15605,7 @@
     <row r="467" ht="65.25" customHeight="1"/>
     <row r="468" ht="16.5" customHeight="1">
       <c t="s" r="A468" s="10">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="B468" s="10"/>
       <c r="C468" s="10"/>
@@ -15536,7 +15618,7 @@
       <c r="J468" s="10"/>
       <c r="K468" s="10"/>
       <c t="s" r="L468" s="11">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="M468" s="11"/>
       <c r="N468" s="11"/>
